--- a/demo_data/timeline.xlsx
+++ b/demo_data/timeline.xlsx
@@ -459,7 +459,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>99.92</t>
+          <t>100.96</t>
         </is>
       </c>
     </row>
@@ -471,7 +471,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>100.47</t>
+          <t>101.16</t>
         </is>
       </c>
     </row>
@@ -483,7 +483,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>99.75</t>
+          <t>100.43</t>
         </is>
       </c>
     </row>
@@ -495,7 +495,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>100.73</t>
+          <t>100.34</t>
         </is>
       </c>
     </row>
@@ -507,7 +507,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>100.17</t>
+          <t>100.60</t>
         </is>
       </c>
     </row>
@@ -519,7 +519,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>99.85</t>
+          <t>101.08</t>
         </is>
       </c>
     </row>
@@ -531,7 +531,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>99.83</t>
+          <t>100.45</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>99.69</t>
+          <t>100.07</t>
         </is>
       </c>
     </row>
@@ -555,7 +555,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>99.49</t>
+          <t>98.77</t>
         </is>
       </c>
     </row>
@@ -567,7 +567,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>100.41</t>
+          <t>99.04</t>
         </is>
       </c>
     </row>
@@ -579,7 +579,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>99.65</t>
+          <t>98.36</t>
         </is>
       </c>
     </row>
@@ -591,7 +591,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>99.74</t>
+          <t>98.32</t>
         </is>
       </c>
     </row>
@@ -603,7 +603,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>99.17</t>
+          <t>98.98</t>
         </is>
       </c>
     </row>
@@ -615,7 +615,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>98.89</t>
+          <t>98.47</t>
         </is>
       </c>
     </row>
@@ -627,7 +627,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>98.99</t>
+          <t>98.19</t>
         </is>
       </c>
     </row>
@@ -639,7 +639,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>97.63</t>
+          <t>99.06</t>
         </is>
       </c>
     </row>
@@ -651,7 +651,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>97.05</t>
+          <t>98.07</t>
         </is>
       </c>
     </row>
@@ -663,7 +663,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>96.18</t>
+          <t>97.80</t>
         </is>
       </c>
     </row>
@@ -675,7 +675,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>95.80</t>
+          <t>98.05</t>
         </is>
       </c>
     </row>
@@ -687,7 +687,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>95.54</t>
+          <t>98.22</t>
         </is>
       </c>
     </row>
@@ -699,7 +699,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>94.96</t>
+          <t>97.26</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -711,7 +716,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>93.89</t>
+          <t>97.41</t>
         </is>
       </c>
     </row>
@@ -723,7 +728,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>94.60</t>
+          <t>96.93</t>
         </is>
       </c>
     </row>
@@ -735,7 +740,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>95.08</t>
+          <t>96.98</t>
         </is>
       </c>
     </row>
@@ -747,7 +752,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>94.16</t>
+          <t>96.68</t>
         </is>
       </c>
     </row>
@@ -759,7 +764,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>93.77</t>
+          <t>96.83</t>
         </is>
       </c>
     </row>
@@ -771,7 +776,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>93.43</t>
+          <t>96.87</t>
         </is>
       </c>
     </row>
@@ -783,7 +788,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>93.37</t>
+          <t>97.25</t>
         </is>
       </c>
     </row>
@@ -795,7 +800,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>93.54</t>
+          <t>96.89</t>
         </is>
       </c>
     </row>
@@ -807,7 +812,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>93.24</t>
+          <t>97.13</t>
         </is>
       </c>
     </row>
@@ -819,7 +824,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>92.46</t>
+          <t>96.18</t>
         </is>
       </c>
     </row>
@@ -831,7 +836,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>93.00</t>
+          <t>96.56</t>
         </is>
       </c>
     </row>
@@ -843,7 +848,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>92.36</t>
+          <t>97.10</t>
         </is>
       </c>
     </row>
@@ -855,7 +860,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>92.87</t>
+          <t>97.56</t>
         </is>
       </c>
     </row>
@@ -867,7 +872,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>92.89</t>
+          <t>97.29</t>
         </is>
       </c>
     </row>
@@ -879,7 +884,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>92.96</t>
+          <t>97.60</t>
         </is>
       </c>
     </row>
@@ -891,7 +896,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>92.51</t>
+          <t>96.84</t>
         </is>
       </c>
     </row>
@@ -903,7 +908,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>92.59</t>
+          <t>97.11</t>
         </is>
       </c>
     </row>
@@ -915,7 +920,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>93.27</t>
+          <t>96.21</t>
         </is>
       </c>
     </row>
@@ -927,7 +932,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>93.16</t>
+          <t>95.56</t>
         </is>
       </c>
     </row>
@@ -939,7 +944,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>93.67</t>
+          <t>95.43</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -956,7 +961,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>93.24</t>
+          <t>96.09</t>
         </is>
       </c>
     </row>
@@ -968,7 +973,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>93.37</t>
+          <t>96.15</t>
         </is>
       </c>
     </row>
@@ -980,7 +985,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>93.01</t>
+          <t>97.04</t>
         </is>
       </c>
     </row>
@@ -992,7 +997,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>92.09</t>
+          <t>97.40</t>
         </is>
       </c>
     </row>
@@ -1004,7 +1009,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>92.06</t>
+          <t>97.26</t>
         </is>
       </c>
     </row>
@@ -1016,7 +1021,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>92.17</t>
+          <t>97.66</t>
         </is>
       </c>
     </row>
@@ -1028,7 +1033,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>91.65</t>
+          <t>97.62</t>
         </is>
       </c>
     </row>
@@ -1040,7 +1045,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>92.10</t>
+          <t>97.70</t>
         </is>
       </c>
     </row>
@@ -1052,7 +1057,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>91.61</t>
+          <t>98.07</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1069,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>90.80</t>
+          <t>96.19</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1081,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>91.52</t>
+          <t>97.45</t>
         </is>
       </c>
     </row>
@@ -1088,7 +1093,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>91.75</t>
+          <t>98.57</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1105,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>91.35</t>
+          <t>97.72</t>
         </is>
       </c>
     </row>
@@ -1112,7 +1117,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>91.73</t>
+          <t>97.98</t>
         </is>
       </c>
     </row>
@@ -1124,7 +1129,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>92.03</t>
+          <t>98.37</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1141,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>91.60</t>
+          <t>98.95</t>
         </is>
       </c>
     </row>
@@ -1148,7 +1153,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>92.19</t>
+          <t>99.23</t>
         </is>
       </c>
     </row>
@@ -1160,7 +1165,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>91.96</t>
+          <t>98.42</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1177,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>92.85</t>
+          <t>97.36</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1189,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>92.50</t>
+          <t>97.32</t>
         </is>
       </c>
     </row>
@@ -1196,7 +1201,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>92.25</t>
+          <t>97.47</t>
         </is>
       </c>
     </row>
@@ -1208,7 +1213,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>91.69</t>
+          <t>98.44</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1225,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>91.40</t>
+          <t>98.34</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1237,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>91.30</t>
+          <t>98.44</t>
         </is>
       </c>
     </row>
@@ -1244,7 +1249,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>91.83</t>
+          <t>98.93</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1266,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>92.61</t>
+          <t>99.24</t>
         </is>
       </c>
     </row>
@@ -1268,7 +1278,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>91.74</t>
+          <t>99.32</t>
         </is>
       </c>
     </row>
@@ -1280,7 +1290,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>91.30</t>
+          <t>100.11</t>
         </is>
       </c>
     </row>
@@ -1292,7 +1302,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>90.82</t>
+          <t>100.57</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1314,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>89.98</t>
+          <t>101.64</t>
         </is>
       </c>
     </row>
@@ -1316,7 +1326,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>90.15</t>
+          <t>102.01</t>
         </is>
       </c>
     </row>
@@ -1328,7 +1338,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>90.38</t>
+          <t>102.44</t>
         </is>
       </c>
     </row>
@@ -1340,7 +1350,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>90.66</t>
+          <t>102.87</t>
         </is>
       </c>
     </row>
@@ -1352,7 +1362,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>90.24</t>
+          <t>103.21</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1374,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>89.75</t>
+          <t>104.26</t>
         </is>
       </c>
     </row>
@@ -1376,7 +1386,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>89.37</t>
+          <t>105.03</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1398,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>88.93</t>
+          <t>105.81</t>
         </is>
       </c>
     </row>
@@ -1400,7 +1410,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>89.48</t>
+          <t>106.53</t>
         </is>
       </c>
     </row>
@@ -1412,7 +1422,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>89.05</t>
+          <t>106.70</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1434,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>88.45</t>
+          <t>107.25</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1446,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>88.25</t>
+          <t>107.39</t>
         </is>
       </c>
     </row>
@@ -1448,7 +1458,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>87.59</t>
+          <t>107.26</t>
         </is>
       </c>
     </row>
@@ -1460,7 +1470,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>87.15</t>
+          <t>108.11</t>
         </is>
       </c>
     </row>
@@ -1472,7 +1482,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>86.55</t>
+          <t>108.87</t>
         </is>
       </c>
     </row>
@@ -1484,12 +1494,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>86.68</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>True</t>
+          <t>107.70</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1506,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>86.05</t>
+          <t>107.01</t>
         </is>
       </c>
     </row>
@@ -1513,7 +1518,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>86.60</t>
+          <t>108.59</t>
         </is>
       </c>
     </row>
@@ -1525,7 +1530,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>86.78</t>
+          <t>109.28</t>
         </is>
       </c>
     </row>
@@ -1537,7 +1542,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>86.63</t>
+          <t>108.54</t>
         </is>
       </c>
     </row>
@@ -1549,7 +1554,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>86.55</t>
+          <t>108.44</t>
         </is>
       </c>
     </row>
@@ -1561,7 +1566,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>86.71</t>
+          <t>109.11</t>
         </is>
       </c>
     </row>
@@ -1573,7 +1578,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>87.18</t>
+          <t>110.17</t>
         </is>
       </c>
     </row>
@@ -1585,7 +1590,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>87.65</t>
+          <t>111.09</t>
         </is>
       </c>
     </row>
@@ -1597,7 +1602,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>87.46</t>
+          <t>111.44</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1614,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>87.27</t>
+          <t>112.09</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1626,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>87.74</t>
+          <t>112.49</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1638,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>87.86</t>
+          <t>113.42</t>
         </is>
       </c>
     </row>
@@ -1645,7 +1650,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>86.79</t>
+          <t>113.26</t>
         </is>
       </c>
     </row>
@@ -1657,7 +1662,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>86.52</t>
+          <t>113.56</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1674,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>86.51</t>
+          <t>114.07</t>
         </is>
       </c>
     </row>
@@ -1681,7 +1686,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>86.54</t>
+          <t>113.61</t>
         </is>
       </c>
     </row>
@@ -1693,7 +1698,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>87.07</t>
+          <t>113.56</t>
         </is>
       </c>
     </row>
@@ -1705,7 +1710,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>86.98</t>
+          <t>113.87</t>
         </is>
       </c>
     </row>
@@ -1717,7 +1722,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>86.79</t>
+          <t>114.01</t>
         </is>
       </c>
     </row>
@@ -1729,7 +1734,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>87.07</t>
+          <t>113.54</t>
         </is>
       </c>
     </row>
@@ -1741,7 +1746,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>87.26</t>
+          <t>113.90</t>
         </is>
       </c>
     </row>
@@ -1753,7 +1758,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>87.20</t>
+          <t>113.07</t>
         </is>
       </c>
     </row>
@@ -1765,7 +1770,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>87.16</t>
+          <t>114.66</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1782,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>87.89</t>
+          <t>114.95</t>
         </is>
       </c>
     </row>
@@ -1789,7 +1794,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>87.86</t>
+          <t>115.52</t>
         </is>
       </c>
     </row>
@@ -1801,7 +1806,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>87.66</t>
+          <t>115.69</t>
         </is>
       </c>
     </row>
@@ -1813,7 +1818,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>87.66</t>
+          <t>114.51</t>
         </is>
       </c>
     </row>
@@ -1825,7 +1830,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>88.18</t>
+          <t>114.92</t>
         </is>
       </c>
     </row>
@@ -1837,7 +1842,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>87.66</t>
+          <t>114.86</t>
         </is>
       </c>
     </row>
@@ -1849,7 +1854,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>87.66</t>
+          <t>114.48</t>
         </is>
       </c>
     </row>
@@ -1861,7 +1866,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>87.62</t>
+          <t>114.10</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1878,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>87.80</t>
+          <t>114.88</t>
         </is>
       </c>
     </row>
@@ -1885,7 +1890,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>87.81</t>
+          <t>115.67</t>
         </is>
       </c>
     </row>
@@ -1897,7 +1902,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>88.36</t>
+          <t>115.45</t>
         </is>
       </c>
     </row>
@@ -1909,7 +1914,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>88.23</t>
+          <t>115.78</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1926,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>87.87</t>
+          <t>116.62</t>
         </is>
       </c>
     </row>
@@ -1933,7 +1938,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>86.43</t>
+          <t>116.53</t>
         </is>
       </c>
     </row>
@@ -1945,7 +1950,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>86.10</t>
+          <t>115.41</t>
         </is>
       </c>
     </row>
@@ -1957,7 +1962,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>86.20</t>
+          <t>115.98</t>
         </is>
       </c>
     </row>
@@ -1969,7 +1974,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>85.49</t>
+          <t>115.87</t>
         </is>
       </c>
     </row>
@@ -1981,7 +1986,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>85.51</t>
+          <t>116.39</t>
         </is>
       </c>
     </row>
@@ -1996,7 +2001,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2019,7 +2024,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-01-02 to 2026-03-01</t>
+          <t>2026-01-02 to 2026-02-01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2028,7 +2033,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="3">
@@ -2038,7 +2043,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="4">
@@ -2048,7 +2053,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="5">
@@ -2058,127 +2063,142 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-02-02 to 2026-03-01</t>
+        </is>
+      </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Hedwig Logistics Ltd</t>
+          <t>Albus Industries Ltd</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-03-02 to 2026-05-03</t>
-        </is>
-      </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Albus Industries Ltd</t>
+          <t>Bellatrix Power Ltd</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" t="inlineStr">
         <is>
-          <t>Bellatrix Power Ltd</t>
+          <t>Cedery Pharma Ltd</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="9">
       <c r="B9" t="inlineStr">
         <is>
-          <t>Cedery Pharma Ltd</t>
+          <t>Dobby Logistics Ltd</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-03-02 to 2026-04-05</t>
+        </is>
+      </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Luna Textiles Ltd</t>
+          <t>Bellatrix Power Ltd</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="11">
       <c r="B11" t="inlineStr">
         <is>
-          <t>Hedwig Logistics Ltd</t>
+          <t>Cedery Pharma Ltd</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2026-05-04 to 2026-06-30</t>
-        </is>
-      </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Albus Industries Ltd</t>
+          <t>Dobby Logistics Ltd</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" t="inlineStr">
         <is>
-          <t>Bellatrix Power Ltd</t>
+          <t>Aragog Textiles Ltd</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.19</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-04-06 to 2026-06-30</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
           <t>Cedery Pharma Ltd</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.19</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" t="inlineStr">
         <is>
-          <t>Luna Textiles Ltd</t>
+          <t>Dobby Logistics Ltd</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.19</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" t="inlineStr">
         <is>
-          <t>Hedwig Logistics Ltd</t>
+          <t>Aragog Textiles Ltd</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.19</v>
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Buckbeak Aviation Ltd</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>0.25</v>
       </c>
     </row>
   </sheetData>

--- a/demo_data/timeline.xlsx
+++ b/demo_data/timeline.xlsx
@@ -2049,7 +2049,7 @@
     <row r="4">
       <c r="B4" t="inlineStr">
         <is>
-          <t>Cedery Pharma Ltd</t>
+          <t>Cedric Pharma Ltd</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -2094,7 +2094,7 @@
     <row r="8">
       <c r="B8" t="inlineStr">
         <is>
-          <t>Cedery Pharma Ltd</t>
+          <t>Cedric Pharma Ltd</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -2129,7 +2129,7 @@
     <row r="11">
       <c r="B11" t="inlineStr">
         <is>
-          <t>Cedery Pharma Ltd</t>
+          <t>Cedric Pharma Ltd</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Cedery Pharma Ltd</t>
+          <t>Cedric Pharma Ltd</t>
         </is>
       </c>
       <c r="C14" t="n">
